--- a/data/trans_orig/POLIPATOLOGIA_5-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2007</t>
+          <t>Población con cinco o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>959686</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>961553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730464</t>
+          <t>730444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604537</t>
+          <t>605517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619963</t>
+          <t>619580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1339324</t>
+          <t>1340449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354928</t>
+          <t>1354860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627675</t>
+          <t>627353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636789</t>
+          <t>636757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668043</t>
+          <t>667440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682016</t>
+          <t>681773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300341</t>
+          <t>1299712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316739</t>
+          <t>1316259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38395</t>
+          <t>36644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498992</t>
+          <t>499167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513536</t>
+          <t>513434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>477247</t>
+          <t>478998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497682</t>
+          <t>497905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>982560</t>
+          <t>983791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1008419</t>
+          <t>1007685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>55621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52912</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81953</t>
+          <t>81550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352463</t>
+          <t>352920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>371366</t>
+          <t>371878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>349476</t>
+          <t>348365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>372469</t>
+          <t>372661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708743</t>
+          <t>709146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737784</t>
+          <t>738809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>26298</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48123</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>45495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>72653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78010</t>
+          <t>77387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112524</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244460</t>
+          <t>243568</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266665</t>
+          <t>266285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270148</t>
+          <t>270281</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298604</t>
+          <t>297439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522993</t>
+          <t>523374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>557507</t>
+          <t>558130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60313</t>
+          <t>62052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92929</t>
+          <t>93423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92111</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131405</t>
+          <t>132533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162350</t>
+          <t>163309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184516</t>
+          <t>183957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>240485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>273595</t>
+          <t>271856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>412386</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>451680</t>
+          <t>450838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92695</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198422</t>
+          <t>199560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260679</t>
+          <t>258014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>306644</t>
+          <t>303891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3141706</t>
+          <t>3140422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3183848</t>
+          <t>3181917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3118518</t>
+          <t>3121183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3180775</t>
+          <t>3179637</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6277312</t>
+          <t>6281645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6349097</t>
+          <t>6351850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449177</t>
+          <t>449321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425038</t>
+          <t>425262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877606</t>
+          <t>877486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682153</t>
+          <t>681953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594912</t>
+          <t>594084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607566</t>
+          <t>607524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280205</t>
+          <t>1280021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294378</t>
+          <t>1293718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32764</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673841</t>
+          <t>672726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680974</t>
+          <t>680976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>678086</t>
+          <t>677856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>696679</t>
+          <t>696296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1354704</t>
+          <t>1356627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1376547</t>
+          <t>1376066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28807</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>54283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70346</t>
+          <t>70771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590412</t>
+          <t>591772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608196</t>
+          <t>607290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562057</t>
+          <t>561916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587392</t>
+          <t>588596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160470</t>
+          <t>1160045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190144</t>
+          <t>1191877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55204</t>
+          <t>55052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87038</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70209</t>
+          <t>71616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107705</t>
+          <t>108643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401993</t>
+          <t>402525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418548</t>
+          <t>418826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>360762</t>
+          <t>360471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392596</t>
+          <t>392748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>769524</t>
+          <t>768586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807020</t>
+          <t>805613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31270</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58042</t>
+          <t>59373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>87799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96610</t>
+          <t>97725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136648</t>
+          <t>137394</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251744</t>
+          <t>250413</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278516</t>
+          <t>277414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266768</t>
+          <t>266197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296080</t>
+          <t>295949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527134</t>
+          <t>526388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>567172</t>
+          <t>566057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38745</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64789</t>
+          <t>67295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119306</t>
+          <t>117609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157204</t>
+          <t>156652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166937</t>
+          <t>166172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214373</t>
+          <t>213604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185062</t>
+          <t>182556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211106</t>
+          <t>210886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231775</t>
+          <t>232327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269673</t>
+          <t>271370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>424457</t>
+          <t>425226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471893</t>
+          <t>472658</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107465</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153734</t>
+          <t>156398</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>313531</t>
+          <t>316576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>388151</t>
+          <t>388206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>438667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>523549</t>
+          <t>522074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3273045</t>
+          <t>3270381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3319314</t>
+          <t>3319811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3170158</t>
+          <t>3170103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3244778</t>
+          <t>3241733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6461539</t>
+          <t>6463014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6548774</t>
+          <t>6546421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>959</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5775</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390949</t>
+          <t>390912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810403</t>
+          <t>809443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551204</t>
+          <t>550245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561274</t>
+          <t>561511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141233</t>
+          <t>1141043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152106</t>
+          <t>1151691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660072</t>
+          <t>660537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637186</t>
+          <t>636681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652038</t>
+          <t>652073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1302616</t>
+          <t>1303613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319371</t>
+          <t>1319424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>59872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>46835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78678</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618910</t>
+          <t>620249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636565</t>
+          <t>636828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589966</t>
+          <t>589205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617056</t>
+          <t>615410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1216447</t>
+          <t>1215042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1246671</t>
+          <t>1248290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62321</t>
+          <t>61828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>94760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126362</t>
+          <t>123732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440048</t>
+          <t>439758</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461766</t>
+          <t>462089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398817</t>
+          <t>402089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>434528</t>
+          <t>435021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848405</t>
+          <t>851035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889690</t>
+          <t>892062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72754</t>
+          <t>73360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96549</t>
+          <t>98430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136057</t>
+          <t>138858</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294659</t>
+          <t>294967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314655</t>
+          <t>314753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271272</t>
+          <t>269339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305008</t>
+          <t>304402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>576035</t>
+          <t>573234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615543</t>
+          <t>613662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>93268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133955</t>
+          <t>132664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138678</t>
+          <t>137693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184592</t>
+          <t>184578</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198469</t>
+          <t>195995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220510</t>
+          <t>220318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>266214</t>
+          <t>267505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306885</t>
+          <t>306901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472575</t>
+          <t>472589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518489</t>
+          <t>519474</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97702</t>
+          <t>99319</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142580</t>
+          <t>143874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>310099</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>386289</t>
+          <t>390815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>420266</t>
+          <t>422978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>508712</t>
+          <t>509744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3251770</t>
+          <t>3250476</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3296648</t>
+          <t>3295031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3158253</t>
+          <t>3153727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3234443</t>
+          <t>3232114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6430180</t>
+          <t>6429148</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6518626</t>
+          <t>6515914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>398962</t>
+          <t>399010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295503</t>
+          <t>295021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311571</t>
+          <t>311529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695043</t>
+          <t>695355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711282</t>
+          <t>711492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415402</t>
+          <t>415084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489938</t>
+          <t>489153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505996</t>
+          <t>505638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911167</t>
+          <t>911019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927618</t>
+          <t>927147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35900</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58117</t>
+          <t>57334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508370</t>
+          <t>508685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525326</t>
+          <t>525580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>556102</t>
+          <t>556439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>574132</t>
+          <t>574273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070223</t>
+          <t>1071006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095969</t>
+          <t>1095066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>65115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112106</t>
+          <t>112100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>83764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171393</t>
+          <t>171439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822398</t>
+          <t>822671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870425</t>
+          <t>871063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600775</t>
+          <t>600781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637937</t>
+          <t>637309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1429274</t>
+          <t>1429228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1519733</t>
+          <t>1516903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50891</t>
+          <t>49791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77413</t>
+          <t>76460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92338</t>
+          <t>93021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119540</t>
+          <t>120434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149498</t>
+          <t>150108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187295</t>
+          <t>190144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>483821</t>
+          <t>484774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>510343</t>
+          <t>511443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428365</t>
+          <t>427471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>455567</t>
+          <t>454884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>921844</t>
+          <t>918995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959641</t>
+          <t>959031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>46061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66736</t>
+          <t>69318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167097</t>
+          <t>167352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>486607</t>
+          <t>476928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212009</t>
+          <t>211523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>653409</t>
+          <t>658543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>301429</t>
+          <t>298847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>322139</t>
+          <t>322104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121761</t>
+          <t>131440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>441271</t>
+          <t>441016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323124</t>
+          <t>317990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>764524</t>
+          <t>765010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83557</t>
+          <t>82564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>106840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>189474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217834</t>
+          <t>218177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318241</t>
+          <t>317171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175183</t>
+          <t>175919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199202</t>
+          <t>200195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207997</t>
+          <t>207654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>237715</t>
+          <t>236357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390349</t>
+          <t>391419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428298</t>
+          <t>429485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>215175</t>
+          <t>214747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>309745</t>
+          <t>311928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>585192</t>
+          <t>584704</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1319657</t>
+          <t>1318188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>832624</t>
+          <t>840275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1690428</t>
+          <t>1625930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3150072</t>
+          <t>3147889</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3244642</t>
+          <t>3245070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2392623</t>
+          <t>2394092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3127088</t>
+          <t>3127576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5481669</t>
+          <t>5546167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6339473</t>
+          <t>6331822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_5-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Edad-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730444</t>
+          <t>730436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605517</t>
+          <t>605609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619580</t>
+          <t>619903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1340449</t>
+          <t>1339032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354860</t>
+          <t>1354782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627353</t>
+          <t>627269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636757</t>
+          <t>636794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667440</t>
+          <t>667802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681773</t>
+          <t>681949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1299712</t>
+          <t>1300553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316259</t>
+          <t>1317216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50998</t>
+          <t>50606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499167</t>
+          <t>499613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513434</t>
+          <t>513978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478998</t>
+          <t>478918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497905</t>
+          <t>498965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>983791</t>
+          <t>984183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1007685</t>
+          <t>1007797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55621</t>
+          <t>54713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>51061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81550</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352920</t>
+          <t>351073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>371878</t>
+          <t>371054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>348365</t>
+          <t>349273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>372661</t>
+          <t>374171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709146</t>
+          <t>710291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738809</t>
+          <t>739635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45495</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72653</t>
+          <t>72704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77387</t>
+          <t>77624</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112143</t>
+          <t>112879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243568</t>
+          <t>245109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266285</t>
+          <t>266531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270281</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>297439</t>
+          <t>297422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523374</t>
+          <t>522638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>558130</t>
+          <t>557893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>25567</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>46358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62052</t>
+          <t>60246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93423</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92953</t>
+          <t>93152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>131969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163309</t>
+          <t>163525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183957</t>
+          <t>184316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240485</t>
+          <t>240872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271856</t>
+          <t>273662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>411258</t>
+          <t>411822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>450838</t>
+          <t>450639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136121</t>
+          <t>132324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199560</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258014</t>
+          <t>259829</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>303891</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374096</t>
+          <t>375812</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3140422</t>
+          <t>3144219</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3181917</t>
+          <t>3184209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3121183</t>
+          <t>3119368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3179637</t>
+          <t>3180309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6281645</t>
+          <t>6279929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6351850</t>
+          <t>6352118</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449321</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425262</t>
+          <t>425319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877486</t>
+          <t>878243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681953</t>
+          <t>682120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594084</t>
+          <t>594872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607524</t>
+          <t>607372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280021</t>
+          <t>1280055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293718</t>
+          <t>1293921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672726</t>
+          <t>672552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680976</t>
+          <t>680951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677856</t>
+          <t>677967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>696296</t>
+          <t>697309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1356627</t>
+          <t>1356612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1376066</t>
+          <t>1376348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54283</t>
+          <t>55793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70771</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591772</t>
+          <t>592022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607290</t>
+          <t>608068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561916</t>
+          <t>560406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>588596</t>
+          <t>586816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160045</t>
+          <t>1160495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191877</t>
+          <t>1191655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55052</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>87009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108643</t>
+          <t>107089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402525</t>
+          <t>401335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418826</t>
+          <t>418786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>360471</t>
+          <t>360791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392748</t>
+          <t>392156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>768586</t>
+          <t>770140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>805613</t>
+          <t>806058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59373</t>
+          <t>58270</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87799</t>
+          <t>87527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97725</t>
+          <t>96212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>138905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250413</t>
+          <t>251516</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277414</t>
+          <t>278745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266197</t>
+          <t>266469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295949</t>
+          <t>298156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526388</t>
+          <t>524877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>566057</t>
+          <t>567570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>37832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117609</t>
+          <t>119416</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156652</t>
+          <t>157821</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166172</t>
+          <t>164757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213604</t>
+          <t>212168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182556</t>
+          <t>185233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210886</t>
+          <t>212019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232327</t>
+          <t>231158</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271370</t>
+          <t>269563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>425226</t>
+          <t>426662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>472658</t>
+          <t>474073</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>107358</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>155302</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>316576</t>
+          <t>318098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>388206</t>
+          <t>393390</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>438667</t>
+          <t>439319</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>522074</t>
+          <t>528206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3270381</t>
+          <t>3271477</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3319811</t>
+          <t>3319421</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3170103</t>
+          <t>3164919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3241733</t>
+          <t>3240211</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6463014</t>
+          <t>6456882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6546421</t>
+          <t>6545769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390912</t>
+          <t>390769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809443</t>
+          <t>809510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550245</t>
+          <t>550268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561511</t>
+          <t>560864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141043</t>
+          <t>1141147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151691</t>
+          <t>1151763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660537</t>
+          <t>661165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636681</t>
+          <t>637032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652073</t>
+          <t>651352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303613</t>
+          <t>1302325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319424</t>
+          <t>1319085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>32068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59872</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46835</t>
+          <t>48187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>78078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>620249</t>
+          <t>620009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636828</t>
+          <t>636689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589205</t>
+          <t>589239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615410</t>
+          <t>617009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1215042</t>
+          <t>1217047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1248290</t>
+          <t>1246938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>37321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61828</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94760</t>
+          <t>95866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82705</t>
+          <t>83742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>125437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439758</t>
+          <t>440597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462089</t>
+          <t>462501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402089</t>
+          <t>400983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435021</t>
+          <t>434428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851035</t>
+          <t>849330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>892062</t>
+          <t>891025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>40318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73360</t>
+          <t>72033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108423</t>
+          <t>107625</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98430</t>
+          <t>97935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>137315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294967</t>
+          <t>294012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314753</t>
+          <t>314535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269339</t>
+          <t>270137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304402</t>
+          <t>305729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573234</t>
+          <t>574777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613662</t>
+          <t>614157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>36628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61003</t>
+          <t>59182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93268</t>
+          <t>91487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132664</t>
+          <t>132462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137693</t>
+          <t>138899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184578</t>
+          <t>186072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195995</t>
+          <t>197816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220318</t>
+          <t>220370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267505</t>
+          <t>267707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306901</t>
+          <t>308682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472589</t>
+          <t>471095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519474</t>
+          <t>518268</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99319</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143874</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312428</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>390815</t>
+          <t>386225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>422978</t>
+          <t>425038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>509744</t>
+          <t>509279</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3250476</t>
+          <t>3252356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3295031</t>
+          <t>3296544</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3153727</t>
+          <t>3158317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3232114</t>
+          <t>3235821</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6429148</t>
+          <t>6429613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6515914</t>
+          <t>6513854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406085</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399010</t>
+          <t>400466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306830</t>
+          <t>355812</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295021</t>
+          <t>343669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311529</t>
+          <t>360465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>706652</t>
+          <t>761897</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695355</t>
+          <t>750180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711492</t>
+          <t>768111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421150</t>
+          <t>474324</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415084</t>
+          <t>467482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489153</t>
+          <t>479316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505638</t>
+          <t>493694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920437</t>
+          <t>961925</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911019</t>
+          <t>952089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927147</t>
+          <t>968730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,67 +10386,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>48607</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>37219</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>62470</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,99%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>43530</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>33274</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>57334</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518680</t>
+          <t>601959</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508685</t>
+          <t>590976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525580</t>
+          <t>609640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,67 +10499,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>566130</t>
+          <t>593464</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>556439</t>
+          <t>584092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>574273</t>
+          <t>601817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1195422</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1181559</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1206810</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,01%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1337</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1084810</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1071006</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1095066</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>45728</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>61452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>95070</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>81541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112100</t>
+          <t>110443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135905</t>
+          <t>140799</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>121053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171439</t>
+          <t>160198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>845519</t>
+          <t>654889</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822671</t>
+          <t>639165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871063</t>
+          <t>667317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>619243</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600781</t>
+          <t>626443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637309</t>
+          <t>655345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1464762</t>
+          <t>1296705</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1429228</t>
+          <t>1277306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1516903</t>
+          <t>1316451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49791</t>
+          <t>52507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>84265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105258</t>
+          <t>115966</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120434</t>
+          <t>131632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>182378</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150108</t>
+          <t>161998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190144</t>
+          <t>204178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>498567</t>
+          <t>542935</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>484774</t>
+          <t>525081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>511443</t>
+          <t>556839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>442647</t>
+          <t>492889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427471</t>
+          <t>477223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454884</t>
+          <t>507577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>941214</t>
+          <t>1035824</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>918995</t>
+          <t>1014024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959031</t>
+          <t>1056204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>320723</t>
+          <t>129034</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167352</t>
+          <t>116657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>476928</t>
+          <t>144436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>376617</t>
+          <t>187563</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>211523</t>
+          <t>170478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>658543</t>
+          <t>206778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>312271</t>
+          <t>348551</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298847</t>
+          <t>337419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>322104</t>
+          <t>359970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>287645</t>
+          <t>310132</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131440</t>
+          <t>294730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>441016</t>
+          <t>322509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>599916</t>
+          <t>658683</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>317990</t>
+          <t>639468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>765010</t>
+          <t>675768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>94189</t>
+          <t>102790</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82564</t>
+          <t>88927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106840</t>
+          <t>116558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>203641</t>
+          <t>221775</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189474</t>
+          <t>204968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218177</t>
+          <t>236129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>297830</t>
+          <t>324565</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279105</t>
+          <t>301156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>345099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>188570</t>
+          <t>207408</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175919</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200195</t>
+          <t>221271</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>222190</t>
+          <t>242834</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207654</t>
+          <t>228480</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>236357</t>
+          <t>259641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>410760</t>
+          <t>450242</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>391419</t>
+          <t>429708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>429485</t>
+          <t>473651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>214747</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>311928</t>
+          <t>326031</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>584704</t>
+          <t>577420</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1318188</t>
+          <t>648180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>840275</t>
+          <t>863262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1625930</t>
+          <t>960896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3184580</t>
+          <t>3236151</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3147889</t>
+          <t>3206731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3245070</t>
+          <t>3263574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2943972</t>
+          <t>3124548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2394092</t>
+          <t>3088774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3127576</t>
+          <t>3159534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6128552</t>
+          <t>6360699</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5546167</t>
+          <t>6308820</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6331822</t>
+          <t>6406454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
